--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_5_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_5_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268863.2053994783</v>
+        <v>284256.2999365503</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928675</v>
+        <v>4921297.203522781</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22243395.367831</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4043011.586045243</v>
+        <v>4061835.96209316</v>
       </c>
     </row>
     <row r="11">
@@ -1843,13 +1843,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.006138603635352</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4.006138603635353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.006138603635352</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2071,19 +2071,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>35.23199999999998</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="U21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2274,28 +2274,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2350,13 +2350,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2444,16 +2444,16 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="25">
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>9.137025436486079</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2481,10 +2481,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>35.23199999999998</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2627,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F27" t="n">
-        <v>35.23199999999997</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="28">
@@ -2742,22 +2742,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U28" t="n">
-        <v>9.137025436486079</v>
+        <v>42.20118209180435</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2824,25 +2824,25 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>28.88091821707973</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G30" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="31">
@@ -2952,16 +2952,16 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2997,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.7904504476822691</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="32">
@@ -3031,16 +3031,16 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>16.93162886246722</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3155,16 +3155,16 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="W33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3180,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.790450447682255</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3228,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>26.86753361060322</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>28.88091821707973</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3313,13 +3313,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>23.28271064538745</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3335,16 +3335,16 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>38.12502610536669</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3465,19 +3465,19 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.790450447682255</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,31 +3535,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>16.93162886246721</v>
       </c>
       <c r="Y38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3617,10 +3617,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3651,13 +3651,13 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.7904504476822691</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3696,16 +3696,16 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>9.137025436486075</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="C41" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3742,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="42">
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3857,25 +3857,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="W42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3939,22 +3939,22 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4.958101428732459</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>13.87230102303341</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.410468283527761</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>13.87230102303341</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4.958101428732459</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>13.87230102303341</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="C20" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="D20" t="n">
-        <v>84.00808080808082</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="E20" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F20" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M20" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N20" t="n">
-        <v>122</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="O20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L21" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M21" t="n">
-        <v>42.8</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N21" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O21" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S21" t="n">
-        <v>124.4121212121212</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T21" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U21" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="V21" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W21" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J22" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L22" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M22" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N22" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R22" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="S22" t="n">
-        <v>133.6414398348344</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="T22" t="n">
-        <v>133.6414398348344</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="U22" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="V22" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W22" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X22" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C23" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D23" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L23" t="n">
-        <v>41.20000000000001</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="M23" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N23" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O23" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q23" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R23" t="n">
-        <v>149.9083846317729</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="T23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X23" t="n">
-        <v>149.9083846317729</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y23" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M24" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N24" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O24" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P24" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R24" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S24" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T24" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U24" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V24" t="n">
-        <v>84.00808080808082</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W24" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X24" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C25" t="n">
-        <v>52.83335902675362</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="D25" t="n">
-        <v>12.42931862271321</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W25" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X25" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y25" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C26" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D26" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L26" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M26" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N26" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S26" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="T26" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U26" t="n">
-        <v>124.4121212121212</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="V26" t="n">
-        <v>124.4121212121212</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="W26" t="n">
-        <v>124.4121212121212</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X26" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y26" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="C27" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="D27" t="n">
-        <v>38.78787878787876</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="E27" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K27" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L27" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M27" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N27" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O27" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L28" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M28" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N28" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P28" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="Q28" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="R28" t="n">
-        <v>93.23739943079403</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="S28" t="n">
-        <v>52.83335902675362</v>
+        <v>90.73598234693722</v>
       </c>
       <c r="T28" t="n">
-        <v>12.42931862271321</v>
+        <v>46.15803044872652</v>
       </c>
       <c r="U28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="V28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C29" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D29" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E29" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F29" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L29" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M29" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N29" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q29" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R29" t="n">
-        <v>119.5959595959596</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S29" t="n">
-        <v>84.00808080808082</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T29" t="n">
-        <v>84.00808080808082</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="U29" t="n">
-        <v>84.00808080808082</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="V29" t="n">
-        <v>84.00808080808082</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="W29" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X29" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y29" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="C30" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D30" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="E30" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F30" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G30" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K30" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L30" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M30" t="n">
-        <v>122</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N30" t="n">
-        <v>160</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O30" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V30" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W30" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X30" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y30" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H31" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I31" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V31" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W31" t="n">
-        <v>133.6414398348344</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X31" t="n">
-        <v>133.6414398348344</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.6414398348344</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="C32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>60.17851493563234</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K32" t="n">
-        <v>41.20000000000001</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L32" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M32" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N32" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="O32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q32" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R32" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S32" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T32" t="n">
-        <v>119.5959595959596</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="U32" t="n">
-        <v>119.5959595959596</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="V32" t="n">
-        <v>119.5959595959596</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="W32" t="n">
-        <v>79.19191919191917</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="X32" t="n">
-        <v>38.78787878787876</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C33" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D33" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F33" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L33" t="n">
-        <v>41.20000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M33" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N33" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O33" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V33" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W33" t="n">
-        <v>119.5959595959596</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="X33" t="n">
-        <v>119.5959595959596</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y33" t="n">
-        <v>79.19191919191917</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.69443618776046</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="C34" t="n">
-        <v>25.69443618776046</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="D34" t="n">
-        <v>25.69443618776046</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="E34" t="n">
-        <v>25.69443618776046</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="F34" t="n">
-        <v>25.69443618776046</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G34" t="n">
-        <v>25.69443618776046</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="H34" t="n">
-        <v>25.69443618776046</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="I34" t="n">
-        <v>25.69443618776046</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="J34" t="n">
-        <v>25.69443618776046</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="L34" t="n">
-        <v>30.51412500771298</v>
+        <v>69.3105240343566</v>
       </c>
       <c r="M34" t="n">
-        <v>69.70216319993516</v>
+        <v>108.4985622265788</v>
       </c>
       <c r="N34" t="n">
-        <v>109.3021631999352</v>
+        <v>152.1894128820151</v>
       </c>
       <c r="O34" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P34" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R34" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S34" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T34" t="n">
-        <v>93.23739943079403</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U34" t="n">
-        <v>93.23739943079403</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V34" t="n">
-        <v>66.09847659180087</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W34" t="n">
-        <v>25.69443618776046</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X34" t="n">
-        <v>25.69443618776046</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y34" t="n">
-        <v>25.69443618776046</v>
+        <v>176.5286895169144</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>55.67402965112376</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C35" t="n">
-        <v>55.67402965112376</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D35" t="n">
-        <v>55.67402965112376</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E35" t="n">
-        <v>55.67402965112376</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F35" t="n">
-        <v>55.67402965112376</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G35" t="n">
-        <v>15.26998924708335</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H35" t="n">
-        <v>15.26998924708335</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I35" t="n">
-        <v>15.26998924708335</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K35" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L35" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M35" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N35" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="U35" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="V35" t="n">
-        <v>136.4821104592046</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="W35" t="n">
-        <v>136.4821104592046</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="X35" t="n">
-        <v>96.07807005516418</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="Y35" t="n">
-        <v>96.07807005516418</v>
+        <v>77.28117035226589</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C36" t="n">
-        <v>124.4121212121212</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D36" t="n">
-        <v>84.00808080808082</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E36" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>4.284706443124001</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K36" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="L36" t="n">
-        <v>42.8</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M36" t="n">
-        <v>42.8</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N36" t="n">
-        <v>42.8</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O36" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P36" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V36" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W36" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X36" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y36" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="C37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>69.3105240343566</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>108.4985622265788</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>152.1894128820151</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P37" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R37" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S37" t="n">
-        <v>133.6414398348344</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T37" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U37" t="n">
-        <v>84.00808080808082</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V37" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="X37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.2</v>
+        <v>41.99639902664363</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>43.60404040404041</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="C38" t="n">
-        <v>43.60404040404041</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="D38" t="n">
-        <v>43.60404040404041</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K38" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L38" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M38" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N38" t="n">
-        <v>80.80000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O38" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q38" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R38" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S38" t="n">
-        <v>119.5959595959596</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T38" t="n">
-        <v>119.5959595959596</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="U38" t="n">
-        <v>119.5959595959596</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="V38" t="n">
-        <v>119.5959595959596</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="W38" t="n">
-        <v>119.5959595959596</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="X38" t="n">
-        <v>119.5959595959596</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="Y38" t="n">
-        <v>79.19191919191917</v>
+        <v>15.60056303742164</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C39" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D39" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="N39" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="O39" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="P39" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R39" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="S39" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="T39" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U39" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V39" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W39" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X39" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y39" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C40" t="n">
-        <v>29.55856016516557</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D40" t="n">
-        <v>29.55856016516557</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K40" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L40" t="n">
-        <v>56.87268517287855</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M40" t="n">
-        <v>96.06072336510073</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N40" t="n">
-        <v>135.6607233651007</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O40" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P40" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q40" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R40" t="n">
-        <v>119.5959595959596</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S40" t="n">
-        <v>110.3666409732464</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="T40" t="n">
-        <v>69.96260056920597</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="U40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="V40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="W40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y40" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>119.5959595959596</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C41" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D41" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E41" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F41" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G41" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K41" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L41" t="n">
-        <v>82.40000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M41" t="n">
-        <v>122</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N41" t="n">
-        <v>160</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O41" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V41" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W41" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="X41" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y41" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C42" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D42" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K42" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L42" t="n">
-        <v>41.20000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="M42" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N42" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O42" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P42" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S42" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="T42" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="U42" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="V42" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W42" t="n">
-        <v>119.5959595959596</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y42" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>43.60404040404041</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T43" t="n">
-        <v>133.6414398348344</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="U43" t="n">
-        <v>133.6414398348344</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="V43" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="W43" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="X43" t="n">
-        <v>124.4121212121212</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="Y43" t="n">
-        <v>84.00808080808082</v>
+        <v>43.15042425981653</v>
       </c>
     </row>
     <row r="44">
@@ -9150,16 +9150,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>234.8945286446607</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>233.9613590139789</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>234.6465068390747</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>235.5975216608439</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9229,16 +9229,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>146.6823293394063</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>135.8900075007213</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>147.1445398618324</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>138.3389333199046</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9305,16 +9305,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>134.8846762812383</v>
+        <v>139.4329716986263</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>143.4740793649931</v>
       </c>
       <c r="N19" t="n">
-        <v>127.6855444652332</v>
+        <v>132.2338398826212</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>142.8210643574171</v>
       </c>
       <c r="P19" t="n">
         <v>135.0065633140411</v>
@@ -9384,16 +9384,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M20" t="n">
-        <v>270.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N20" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O20" t="n">
-        <v>268.4820498055251</v>
+        <v>272.4472657249869</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9463,19 +9463,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N21" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P21" t="n">
-        <v>172.3582457981686</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9621,19 +9621,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>274.1502533538256</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>270.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O23" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P23" t="n">
-        <v>271.2329957552695</v>
+        <v>273.5820500585697</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M24" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>180.9800828282828</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,19 +9855,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M26" t="n">
-        <v>268.7300716111112</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N26" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P26" t="n">
         <v>231.2329957552695</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>177.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L27" t="n">
-        <v>176.9382181637126</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N27" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10095,16 +10095,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
-        <v>274.1502533538256</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M29" t="n">
-        <v>270.3462332272727</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N29" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O29" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P29" t="n">
         <v>231.2329957552695</v>
@@ -10171,22 +10171,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>177.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L30" t="n">
-        <v>178.5543797798742</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M30" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,19 +10329,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>258.4736894288189</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O32" t="n">
-        <v>270.0982114216868</v>
+        <v>272.4472657249869</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10408,22 +10408,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L33" t="n">
-        <v>176.9382181637126</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M33" t="n">
-        <v>182.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N33" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q33" t="n">
         <v>139.9817740860215</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>258.4736894288189</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L35" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O35" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>177.841438974359</v>
+        <v>180.1904932776592</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N36" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>180.9800828282828</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q36" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M38" t="n">
-        <v>268.7300716111112</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O38" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P38" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10891,16 +10891,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>169.7255504671717</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P39" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q39" t="n">
-        <v>179.9817740860215</v>
+        <v>182.3308283893217</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>270.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N41" t="n">
-        <v>267.7969019804293</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L42" t="n">
-        <v>176.9382181637126</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M42" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>171.3417120833333</v>
+        <v>169.3262404810591</v>
       </c>
       <c r="O42" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11207,7 +11207,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23701,13 +23701,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>402.3277503243235</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>410.7544420977471</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>334.9265066983792</v>
       </c>
       <c r="I17" t="n">
         <v>210.4758895704059</v>
@@ -23740,7 +23740,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>205.01393098261</v>
       </c>
       <c r="T17" t="n">
         <v>223.0958495641314</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>132.7952217458226</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>107.6871488191085</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>85.39049424777973</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23816,7 +23816,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>95.60953873525513</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
@@ -23850,10 +23850,10 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>167.2468210986278</v>
+        <v>162.6985256812398</v>
       </c>
       <c r="D19" t="n">
-        <v>148.6154730182124</v>
+        <v>144.0671776008244</v>
       </c>
       <c r="E19" t="n">
         <v>146.4339626465692</v>
@@ -23895,10 +23895,10 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>177.2933913771695</v>
+        <v>173.2872527735341</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>219.4683026195843</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
@@ -23929,19 +23929,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>330.0408917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>314.683041620683</v>
+        <v>315.8114241890584</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>337.7981976930332</v>
       </c>
       <c r="F20" t="n">
-        <v>366.8760457417114</v>
+        <v>362.7438733624829</v>
       </c>
       <c r="G20" t="n">
-        <v>375.302737515135</v>
+        <v>371.1705651359065</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -24056,22 +24056,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>136.4511711038379</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>161.2931112631971</v>
       </c>
       <c r="U21" t="n">
-        <v>185.9413820809748</v>
+        <v>181.8092097017462</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W21" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24111,7 +24111,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>13.13246638939677</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>177.2933913771695</v>
+        <v>133.1612189979409</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T22" t="n">
-        <v>227.9455894282815</v>
+        <v>183.8134170490529</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3190293564909</v>
+        <v>285.5285789088086</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="23">
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>342.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>310.5508692414544</v>
       </c>
       <c r="E23" t="n">
-        <v>341.9303700722618</v>
+        <v>337.7981976930332</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24208,13 +24208,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>105.7369455619211</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>170.1484521546208</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>360.9966378705984</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24257,7 +24257,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>98.47189973158609</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24290,7 +24290,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>60.15783415264313</v>
+        <v>56.02566177341454</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
@@ -24302,16 +24302,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>197.5685871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>211.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>165.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="25">
@@ -24321,16 +24321,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D25" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>137.2969372100831</v>
+        <v>102.3017902673406</v>
       </c>
       <c r="F25" t="n">
         <v>145.4210480229312</v>
@@ -24339,10 +24339,10 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
-        <v>162.2271725074396</v>
+        <v>161.4367220597573</v>
       </c>
       <c r="I25" t="n">
-        <v>155.4504749272583</v>
+        <v>111.3183025480297</v>
       </c>
       <c r="J25" t="n">
         <v>93.35918011667277</v>
@@ -24384,7 +24384,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>342.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24409,7 +24409,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>337.7981976930332</v>
       </c>
       <c r="F26" t="n">
         <v>406.8760457417114</v>
@@ -24451,13 +24451,13 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>173.7880695862454</v>
+        <v>170.1484521546208</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24466,10 +24466,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24485,13 +24485,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>107.4450655646388</v>
+        <v>103.3128931854102</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F27" t="n">
-        <v>109.8372123933839</v>
+        <v>106.1975949617593</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -24533,7 +24533,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
@@ -24548,7 +24548,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>165.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="28">
@@ -24600,22 +24600,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>184.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T28" t="n">
-        <v>187.9455894282815</v>
+        <v>183.8134170490529</v>
       </c>
       <c r="U28" t="n">
-        <v>277.1820039200048</v>
+        <v>244.1178472646865</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>338.601669284252</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24649,10 +24649,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24682,25 +24682,25 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>109.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>173.7880695862454</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>320.3600505003333</v>
       </c>
       <c r="X29" t="n">
         <v>369.731100678469</v>
@@ -24719,22 +24719,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>118.7734630237764</v>
       </c>
       <c r="F30" t="n">
-        <v>105.0692123933839</v>
+        <v>100.9370400141553</v>
       </c>
       <c r="G30" t="n">
-        <v>102.1115171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
@@ -24776,7 +24776,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
         <v>251.6949831609196</v>
@@ -24785,7 +24785,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="31">
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
-        <v>84.22215468018669</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
         <v>22.26949182588285</v>
@@ -24855,16 +24855,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
-        <v>252.137643323828</v>
+        <v>251.3471928761457</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X31" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="32">
@@ -24889,16 +24889,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>398.3711086526678</v>
       </c>
       <c r="H32" t="n">
-        <v>339.4748021157671</v>
+        <v>295.3426297365386</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
@@ -24928,7 +24928,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>183.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
@@ -24937,13 +24937,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>329.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y32" t="n">
-        <v>351.0059386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,10 +24953,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>131.3011836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -24965,10 +24965,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>100.9370400141553</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>93.21134478398204</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25013,16 +25013,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>193.9289697178007</v>
       </c>
       <c r="W33" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y33" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25038,16 +25038,16 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D34" t="n">
-        <v>148.6154730182124</v>
+        <v>104.4833006389838</v>
       </c>
       <c r="E34" t="n">
-        <v>146.4339626465692</v>
+        <v>102.3017902673406</v>
       </c>
       <c r="F34" t="n">
-        <v>145.4210480229312</v>
+        <v>101.2888756437027</v>
       </c>
       <c r="G34" t="n">
-        <v>167.9909793584588</v>
+        <v>167.2005289107765</v>
       </c>
       <c r="H34" t="n">
         <v>162.2271725074396</v>
@@ -25059,7 +25059,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25086,16 +25086,16 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>187.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>225.2701097132248</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>342.7338416634806</v>
+        <v>353.8529234464008</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>321.1407193917789</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25126,7 +25126,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25171,13 +25171,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>304.4695478247475</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X35" t="n">
-        <v>329.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25193,16 +25193,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>137.4764989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>107.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>105.0692123933839</v>
+        <v>106.9441862880172</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25247,16 +25247,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>181.8092097017462</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25323,19 +25323,19 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>218.8085639917954</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
-        <v>246.3190293564909</v>
+        <v>242.1868569772623</v>
       </c>
       <c r="V37" t="n">
-        <v>212.137643323828</v>
+        <v>208.0054709445994</v>
       </c>
       <c r="W37" t="n">
-        <v>246.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X37" t="n">
-        <v>225.7096553890372</v>
+        <v>224.9192049413549</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>347.5018416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
@@ -25357,7 +25357,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
@@ -25372,7 +25372,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,31 +25393,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>352.7994718160018</v>
       </c>
       <c r="Y38" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25427,16 +25427,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
@@ -25448,7 +25448,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>45.26446047218649</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25475,10 +25475,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>61.28621672101858</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
@@ -25493,10 +25493,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>170.5409852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25509,13 +25509,13 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>166.4563706509456</v>
       </c>
       <c r="D40" t="n">
-        <v>148.6154730182124</v>
+        <v>104.4833006389838</v>
       </c>
       <c r="E40" t="n">
-        <v>146.4339626465692</v>
+        <v>102.3017902673406</v>
       </c>
       <c r="F40" t="n">
         <v>145.4210480229312</v>
@@ -25554,16 +25554,16 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>214.8795726004862</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T40" t="n">
-        <v>187.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>342.7338416634806</v>
+        <v>347.8683628354914</v>
       </c>
       <c r="C41" t="n">
-        <v>330.0408917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25600,10 +25600,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>299.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25645,16 +25645,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>327.7522584701349</v>
+        <v>288.1683815082943</v>
       </c>
       <c r="W41" t="n">
-        <v>349.240968717413</v>
+        <v>309.6570917555724</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="42">
@@ -25673,7 +25673,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>122.413080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25715,25 +25715,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>132.0992941419972</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>160.580851732981</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>186.3575051191342</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>197.9351083214361</v>
       </c>
       <c r="W42" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25743,10 +25743,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C43" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
         <v>148.6154730182124</v>
@@ -25764,7 +25764,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I43" t="n">
-        <v>155.4504749272583</v>
+        <v>115.8665979654177</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -25797,22 +25797,22 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>227.9455894282815</v>
+        <v>217.9680370670172</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>246.7351523946503</v>
       </c>
       <c r="V43" t="n">
-        <v>252.137643323828</v>
+        <v>212.5537663619874</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>216.5726299525511</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333272.9571474838</v>
+        <v>337273.9246406118</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367487.1572431742</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367487.1572431742</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367487.1572431741</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367487.1572431741</v>
+        <v>370675.4602057996</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367487.1572431741</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367487.1572431742</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367487.1572431741</v>
+        <v>370675.4602057997</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367487.1572431742</v>
+        <v>367166.0848885817</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="E2" t="n">
         <v>69879.81359544017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>69879.81359544017</v>
-      </c>
-      <c r="D2" t="n">
-        <v>69879.81359544015</v>
-      </c>
-      <c r="E2" t="n">
-        <v>69879.81359544015</v>
       </c>
       <c r="F2" t="n">
         <v>69879.81359544017</v>
       </c>
       <c r="G2" t="n">
-        <v>69879.81359544017</v>
+        <v>70717.35472484786</v>
       </c>
       <c r="H2" t="n">
-        <v>77042.03119384474</v>
+        <v>77709.45347827919</v>
       </c>
       <c r="I2" t="n">
-        <v>77042.03119384476</v>
+        <v>77709.45347827919</v>
       </c>
       <c r="J2" t="n">
-        <v>77042.03119384476</v>
+        <v>77709.45347827917</v>
       </c>
       <c r="K2" t="n">
-        <v>77042.03119384476</v>
+        <v>77709.45347827917</v>
       </c>
       <c r="L2" t="n">
-        <v>77042.03119384476</v>
+        <v>77709.45347827916</v>
       </c>
       <c r="M2" t="n">
-        <v>77042.03119384477</v>
+        <v>77709.45347827916</v>
       </c>
       <c r="N2" t="n">
-        <v>77042.03119384476</v>
+        <v>77709.45347827919</v>
       </c>
       <c r="O2" t="n">
-        <v>77042.03119384476</v>
+        <v>76974.81962490581</v>
       </c>
       <c r="P2" t="n">
-        <v>69879.81359544017</v>
+        <v>69879.81359544014</v>
       </c>
     </row>
     <row r="3">
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1246.619549474791</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>10680.08625919725</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
       <c r="C4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
       <c r="D4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
       <c r="E4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
       <c r="F4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
       <c r="G4" t="n">
-        <v>26876.8513828616</v>
+        <v>25424.08254338809</v>
       </c>
       <c r="H4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="I4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="J4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="K4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="L4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="M4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="N4" t="n">
-        <v>29721.20957613287</v>
+        <v>28020.81197764722</v>
       </c>
       <c r="O4" t="n">
-        <v>29721.20957613287</v>
+        <v>27747.98325801255</v>
       </c>
       <c r="P4" t="n">
-        <v>26876.8513828616</v>
+        <v>25113.03606366435</v>
       </c>
     </row>
     <row r="5">
@@ -26432,31 +26432,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>276.5363613771906</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.36221257857</v>
+        <v>11139.17753177579</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.36221257857</v>
+        <v>11139.17753177579</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.362212578555</v>
+        <v>11139.17753177579</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257855</v>
+        <v>44766.77753177582</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257857</v>
+        <v>44766.77753177582</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257857</v>
+        <v>43770.11627060779</v>
       </c>
       <c r="H6" t="n">
-        <v>34096.46161771187</v>
+        <v>36325.31916077761</v>
       </c>
       <c r="I6" t="n">
-        <v>44888.82161771189</v>
+        <v>47005.40541997486</v>
       </c>
       <c r="J6" t="n">
-        <v>44888.82161771188</v>
+        <v>47005.40541997486</v>
       </c>
       <c r="K6" t="n">
-        <v>44888.82161771188</v>
+        <v>47005.40541997485</v>
       </c>
       <c r="L6" t="n">
-        <v>44888.82161771189</v>
+        <v>47005.40541997484</v>
       </c>
       <c r="M6" t="n">
-        <v>44888.8216177119</v>
+        <v>47005.40541997484</v>
       </c>
       <c r="N6" t="n">
-        <v>44888.82161771189</v>
+        <v>47005.40541997486</v>
       </c>
       <c r="O6" t="n">
-        <v>44888.82161771189</v>
+        <v>46820.13664761335</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257857</v>
+        <v>44766.77753177579</v>
       </c>
     </row>
   </sheetData>
@@ -26742,31 +26742,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26959,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
   </sheetData>
@@ -35805,16 +35805,16 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35884,16 +35884,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -35960,16 +35960,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -36039,16 +36039,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O20" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36118,19 +36118,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P21" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36276,19 +36276,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,19 +36510,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M26" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L27" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36750,16 +36750,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M29" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36826,22 +36826,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,19 +36984,19 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O32" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L33" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M33" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37458,22 +37458,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M38" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37546,16 +37546,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N41" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L42" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
